--- a/data/trans_camb/IP42B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 18,24</t>
+          <t>-5,0; 18,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 9,62</t>
+          <t>-9,0; 10,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 15,37</t>
+          <t>-2,44; 15,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 16,25</t>
+          <t>-0,29; 17,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 13,28</t>
+          <t>-0,31; 13,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 11,74</t>
+          <t>-0,83; 12,4</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-81,11; —</t>
+          <t>-66,98; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,03; —</t>
+          <t>-79,31; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,11; —</t>
+          <t>-43,35; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 927,07</t>
+          <t>-17,57; 913,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 817,12</t>
+          <t>-23,81; 977,76</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 19,32</t>
+          <t>-2,48; 19,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 6,32</t>
+          <t>-11,57; 5,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 15,01</t>
+          <t>-2,45; 15,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 9,7</t>
+          <t>-4,49; 9,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 13,27</t>
+          <t>-0,45; 13,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 6,1</t>
+          <t>-5,32; 6,19</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 483,38</t>
+          <t>-24,57; 488,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,34; 171,78</t>
+          <t>-75,74; 188,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 897,89</t>
+          <t>-45,0; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,18; 623,42</t>
+          <t>-61,11; 707,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 334,8</t>
+          <t>-8,1; 374,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 144,53</t>
+          <t>-52,21; 176,02</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 22,57</t>
+          <t>-3,84; 22,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 8,35</t>
+          <t>-16,25; 8,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 26,04</t>
+          <t>-3,1; 25,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 2,37</t>
+          <t>-20,47; 2,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 20,12</t>
+          <t>1,21; 21,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 2,95</t>
+          <t>-13,2; 2,72</t>
         </is>
       </c>
     </row>
@@ -1019,17 +1019,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 489,72</t>
+          <t>-21,61; 578,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,28; 215,5</t>
+          <t>-76,49; 214,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-25,95; 700,76</t>
+          <t>-22,32; 775,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 344,59</t>
+          <t>0,1; 352,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,32; 59,26</t>
+          <t>-77,07; 51,75</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 14,38</t>
+          <t>-10,04; 14,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 11,38</t>
+          <t>-10,13; 10,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 14,21</t>
+          <t>-6,66; 15,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 4,38</t>
+          <t>-13,25; 4,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 11,0</t>
+          <t>-5,27; 10,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 4,72</t>
+          <t>-9,28; 4,32</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-71,93; 375,37</t>
+          <t>-66,78; 413,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-69,76; 370,93</t>
+          <t>-70,85; 273,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,44; 226,46</t>
+          <t>-49,23; 269,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-88,2; 104,49</t>
+          <t>-84,14; 120,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,95; 178,59</t>
+          <t>-41,04; 166,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,96; 87,06</t>
+          <t>-65,48; 66,97</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 12,94</t>
+          <t>0,77; 12,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,78</t>
+          <t>-5,82; 4,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 12,01</t>
+          <t>1,41; 12,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 4,26</t>
+          <t>-4,3; 4,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,42</t>
+          <t>2,82; 10,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,09</t>
+          <t>-3,69; 3,22</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,9; 202,66</t>
+          <t>5,64; 216,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 61,13</t>
+          <t>-46,56; 78,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,6; 221,98</t>
+          <t>9,34; 232,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 85,14</t>
+          <t>-41,96; 104,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,3; 168,19</t>
+          <t>27,35; 163,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 49,73</t>
+          <t>-35,4; 49,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 18,58</t>
+          <t>-4,89; 19,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 10,6</t>
+          <t>-10,06; 9,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 15,44</t>
+          <t>-2,78; 16,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 17,1</t>
+          <t>-1,53; 16,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 13,76</t>
+          <t>-0,59; 14,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 12,4</t>
+          <t>-1,72; 10,86</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-66,98; —</t>
+          <t>-69,68; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-79,31; —</t>
+          <t>-71,18; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,35; —</t>
+          <t>-50,91; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 913,5</t>
+          <t>-27,13; 901,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 977,76</t>
+          <t>-33,45; 823,03</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 19,89</t>
+          <t>-3,56; 19,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 5,86</t>
+          <t>-10,51; 6,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 15,2</t>
+          <t>-1,61; 15,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 9,93</t>
+          <t>-5,58; 9,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 13,72</t>
+          <t>0,5; 14,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 6,19</t>
+          <t>-4,85; 6,69</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 488,81</t>
+          <t>-33,9; 425,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 188,16</t>
+          <t>-75,21; 170,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-45,0; —</t>
+          <t>-39,78; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 707,43</t>
+          <t>-71,29; 592,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 374,42</t>
+          <t>-0,78; 424,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,21; 176,02</t>
+          <t>-46,95; 232,09</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 22,32</t>
+          <t>-3,39; 22,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 8,25</t>
+          <t>-14,36; 7,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 25,82</t>
+          <t>-2,21; 25,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 2,49</t>
+          <t>-20,08; 1,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 21,34</t>
+          <t>0,89; 20,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,2; 2,72</t>
+          <t>-13,16; 2,17</t>
         </is>
       </c>
     </row>
@@ -1019,17 +1019,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 578,19</t>
+          <t>-27,3; 487,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,49; 214,21</t>
+          <t>-75,37; 223,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 775,02</t>
+          <t>-27,1; 690,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 352,85</t>
+          <t>-1,16; 338,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,07; 51,75</t>
+          <t>-79,56; 53,95</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 14,32</t>
+          <t>-11,06; 13,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 10,21</t>
+          <t>-10,57; 10,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 15,14</t>
+          <t>-6,17; 14,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,25; 4,51</t>
+          <t>-13,37; 4,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 10,61</t>
+          <t>-5,19; 9,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 4,32</t>
+          <t>-9,3; 4,94</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 413,18</t>
+          <t>-70,92; 356,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,85; 273,57</t>
+          <t>-68,69; 261,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,23; 269,69</t>
+          <t>-51,44; 268,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-84,14; 120,01</t>
+          <t>-84,47; 112,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,04; 166,16</t>
+          <t>-40,74; 155,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 66,97</t>
+          <t>-61,64; 81,34</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 12,58</t>
+          <t>0,43; 12,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 4,45</t>
+          <t>-5,84; 4,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,11</t>
+          <t>1,31; 12,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 4,65</t>
+          <t>-4,39; 4,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,81</t>
+          <t>2,55; 10,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,22</t>
+          <t>-4,04; 2,78</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,64; 216,23</t>
+          <t>1,69; 193,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 78,74</t>
+          <t>-48,64; 80,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,34; 232,08</t>
+          <t>10,13; 241,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 104,87</t>
+          <t>-43,95; 93,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,35; 163,49</t>
+          <t>24,33; 172,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 49,55</t>
+          <t>-38,64; 44,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,66</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>6,63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1,51</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,14</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,66</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 19,3</t>
+          <t>-3,01; 15,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 9,6</t>
+          <t>-1,25; 16,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 16,07</t>
+          <t>-4,42; 18,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 16,02</t>
+          <t>-9,09; 9,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 14,38</t>
+          <t>-0,63; 13,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 10,86</t>
+          <t>-1,31; 11,74</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>168,1%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>209,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>126,08%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>28,69%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>168,1%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>209,89%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,68; —</t>
+          <t>-76,03; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-42,11; —</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-81,11; —</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-71,18; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-50,91; —</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 901,49</t>
+          <t>-19,73; 927,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 823,03</t>
+          <t>-32,7; 817,12</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,45</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,96</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>7,76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-1,89</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,45</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 19,04</t>
+          <t>-1,97; 15,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 6,14</t>
+          <t>-5,42; 9,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 15,28</t>
+          <t>-2,4; 19,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 9,85</t>
+          <t>-10,66; 6,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 14,58</t>
+          <t>-0,21; 13,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 6,69</t>
+          <t>-6,41; 6,1</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>131,49%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60,33%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>82,12%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-20,02%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>131,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>60,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 425,22</t>
+          <t>-36,61; 897,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,21; 170,49</t>
+          <t>-67,18; 623,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,78; —</t>
+          <t>-22,41; 483,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 592,95</t>
+          <t>-73,34; 171,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 424,58</t>
+          <t>-7,31; 334,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 232,09</t>
+          <t>-58,42; 144,53</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-6,84</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>9,49</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-2,04</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-6,84</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 22,77</t>
+          <t>-1,84; 26,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 7,58</t>
+          <t>-20,67; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 25,72</t>
+          <t>-3,11; 22,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 1,48</t>
+          <t>-14,26; 8,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 20,66</t>
+          <t>0,91; 20,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 2,17</t>
+          <t>-13,04; 2,95</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116,32%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-63,67%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>83,96%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-18,03%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>116,32%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-63,67%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 487,83</t>
+          <t>-25,95; 700,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-75,37; 223,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,1; 690,85</t>
+          <t>-26,83; 489,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-79,28; 215,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 338,46</t>
+          <t>-1,34; 344,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,56; 53,95</t>
+          <t>-76,32; 59,26</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,05</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>2,27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,22</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-4,05</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 13,99</t>
+          <t>-7,12; 14,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 10,93</t>
+          <t>-13,19; 4,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 14,69</t>
+          <t>-10,74; 14,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 4,47</t>
+          <t>-10,98; 11,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 9,96</t>
+          <t>-5,18; 11,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 4,94</t>
+          <t>-9,37; 4,72</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>30,22%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-39,2%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>22,74%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2,22%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-39,2%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 356,27</t>
+          <t>-51,44; 226,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 261,76</t>
+          <t>-88,2; 104,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,44; 268,19</t>
+          <t>-71,93; 375,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-84,47; 112,21</t>
+          <t>-69,76; 370,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 155,63</t>
+          <t>-39,95; 178,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,64; 81,34</t>
+          <t>-63,96; 87,06</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>6,61</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,76</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6,72</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 12,48</t>
+          <t>1,05; 12,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 4,53</t>
+          <t>-4,21; 4,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,76</t>
+          <t>0,68; 12,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,38</t>
+          <t>-5,97; 3,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,68</t>
+          <t>2,55; 10,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,78</t>
+          <t>-3,99; 3,09</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>71,93%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-8,26%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,69; 193,66</t>
+          <t>5,6; 221,98</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 80,72</t>
+          <t>-43,68; 85,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10,13; 241,51</t>
+          <t>3,9; 202,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 93,75</t>
+          <t>-50,08; 61,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,33; 172,16</t>
+          <t>20,3; 168,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 44,13</t>
+          <t>-38,31; 49,73</t>
         </is>
       </c>
     </row>
